--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3191-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3191-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8979F76D-6C54-4546-8647-F8DA057040E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E14D714A-F796-4EAF-8A75-9CD3475F5F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E32CC9D2-FF8E-4E49-82ED-143D79B6ECB2}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{78766B84-EAB9-4D9F-B211-D58A96462BC8}"/>
   </bookViews>
   <sheets>
     <sheet name="3191-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1400,16 +1400,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3443DF01-C85C-4942-9A17-5DAE22500D49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98977AAF-9963-4853-9279-E97DEB17AB6B}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="17" width="9.125" customWidth="1"/>
+    <col min="18" max="18" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1437,7 +1437,7 @@
       <c r="Q1" s="27"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="30"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1563,7 +1563,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>2025</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>2024</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>2023</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>2022</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="34">
         <v>2021</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2020</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>2019</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>2018</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>2017</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>2016</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>2015</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>2014</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>2013</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>2012</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>2011</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>2010</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="34">
         <v>2009</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>2008</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="34">
         <v>2007</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>2006</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="34">
         <v>2005</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>2004</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="34">
         <v>2003</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
         <v>25</v>
       </c>
